--- a/Summer_2026_Semester/datasets/banana.xlsx
+++ b/Summer_2026_Semester/datasets/banana.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:H20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,7 +410,7 @@
         <v>Model Used</v>
       </c>
       <c r="D1" t="str">
-        <v>Dataset Type</v>
+        <v>Dataset</v>
       </c>
       <c r="E1" t="str">
         <v>Accuracy</v>
@@ -420,6 +420,9 @@
       </c>
       <c r="G1" t="str">
         <v>URL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>main challenge</v>
       </c>
     </row>
     <row r="2">
@@ -436,7 +439,7 @@
         <v>https://www.kaggle.com/datasets/shifatearman/bananalsd</v>
       </c>
       <c r="E2" t="str">
-        <v>RGB 99.16</v>
+        <v>RGB 99.16, Night vision 98.02, infrared vision 96.05, thermal vision 96.10</v>
       </c>
       <c r="F2" t="str">
         <v>WILEY, analytical science</v>
@@ -444,6 +447,9 @@
       <c r="G2" t="str">
         <v>https://analyticalsciencejournals.onlinelibrary.wiley.com/doi/epdf/10.1002/jemt.24681</v>
       </c>
+      <c r="H2" t="str">
+        <v>Validation Sensitivity, Data Variability, Need for Fine-Tuning</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -459,12 +465,15 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>Night vision 98.02</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v/>
       </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
@@ -482,12 +491,15 @@
         <v/>
       </c>
       <c r="E4" t="str">
-        <v>infrared vision 96.05</v>
+        <v/>
       </c>
       <c r="F4" t="str">
         <v/>
       </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
@@ -505,59 +517,68 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>thermal vision 96.10</v>
+        <v/>
       </c>
       <c r="F5" t="str">
         <v/>
       </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v/>
+        <v xml:space="preserve">Ibrahim Alrashdi, Marwa Sharawi, Ahmed M. Ali, Karam M. Sallam, Bilal Arain &amp; Mohamed Abdel-Basset </v>
+      </c>
+      <c r="B6">
+        <v>46054</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>(CNN), DenseNet121, EfficientNetB3, Xception, and ResNet50</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>https://www.kaggle.com/datasets/shifatearman/bananalsd</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>96.25%, 99.14%, 96.17%, 94.06%, 96.72%, and 99.33% for the CNN, EfficientNetB3, ResNet50, DenseNet121, ResNet50, and EfficientNetB3 models</v>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>Scientific reports</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>https://www.nature.com/articles/s41598-026-38259-3</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Environmental Variability, Data Constraints, Domain Shift</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v/>
+        <v>Muhammad Khalid Hamid, Said Khalid Shah, Ghassan Husnain, Yazeed Yasin Ghadi, Shahab Ahmad Al Maaytah, Ayman Qahmash</v>
+      </c>
+      <c r="B7">
+        <v>45658</v>
       </c>
       <c r="C7" t="str">
-        <v/>
+        <v>VGG16, MobileNetV2, Xception, and ResNet</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>PlantVillage</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v xml:space="preserve"> 99% accuracy</v>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>WILEY</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>https://onlinelibrary.wiley.com/doi/full/10.1002/eng2.13113</v>
+      </c>
+      <c r="H7" t="str">
+        <v xml:space="preserve">Environmental Variability, Data Quality and Diversity, Subtle Symptom Detection, Domain Shift </v>
       </c>
     </row>
     <row r="8">
@@ -582,6 +603,9 @@
       <c r="G8" t="str">
         <v/>
       </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -605,6 +629,9 @@
       <c r="G9" t="str">
         <v/>
       </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -628,6 +655,9 @@
       <c r="G10" t="str">
         <v/>
       </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -651,6 +681,9 @@
       <c r="G11" t="str">
         <v/>
       </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -674,6 +707,9 @@
       <c r="G12" t="str">
         <v/>
       </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -697,6 +733,9 @@
       <c r="G13" t="str">
         <v/>
       </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -720,6 +759,9 @@
       <c r="G14" t="str">
         <v/>
       </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -743,6 +785,9 @@
       <c r="G15" t="str">
         <v/>
       </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -766,6 +811,9 @@
       <c r="G16" t="str">
         <v/>
       </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -789,6 +837,9 @@
       <c r="G17" t="str">
         <v/>
       </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -812,6 +863,9 @@
       <c r="G18" t="str">
         <v/>
       </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -835,6 +889,9 @@
       <c r="G19" t="str">
         <v/>
       </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -858,10 +915,13 @@
       <c r="G20" t="str">
         <v/>
       </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H20"/>
   </ignoredErrors>
 </worksheet>
 </file>